--- a/hw6/testcases/HW06_TestCases_23127344.xlsx
+++ b/hw6/testcases/HW06_TestCases_23127344.xlsx
@@ -786,15 +786,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -828,6 +830,16 @@
           <t>Expected (status + body)</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Nhan kiem toan</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Ly do (nguoi ra soat)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -860,6 +872,16 @@
           <t>200 · {"message":"Profile updated"}</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -892,6 +914,16 @@
           <t>200 · {"message":"Profile updated"} (không có validate)</t>
         </is>
       </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Không assert điều quan trọng nhất: server.js:121-122 ghi name vô điều kiện, nên bỏ trường sẽ ghi đè giá trị cũ chứ không giữ nguyên. TC như AI viết vẫn pass kể cả khi SUT hành xử đúng lẫn sai.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -924,6 +956,16 @@
           <t>200 · {"message":"Profile updated"}</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -956,6 +998,16 @@
           <t>200 · {"message":"Profile updated"}; GET trả name="12345" (chuỗi — TEXT affinity ép số)</t>
         </is>
       </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Một TC có hai kết quả mong đợi loại trừ nhau thì không thể đánh giá pass/fail — vi phạm nguyên tắc cơ bản của test case. AI viết vậy vì không suy được hành vi bind kiểu của sqlite3 chỉ từ server.js:122. Tôi chạy thật: name:12345 → 200, và GET trả về name:"12345" — SQLite TEXT affinity ép số thành chuỗi.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -988,6 +1040,16 @@
           <t>200 · {"message":"Profile updated"}</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Cùng lý do</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1020,6 +1082,16 @@
           <t>200; GET trả shipping_address="[object Object]" — hỏng dữ liệu thầm lặng</t>
         </is>
       </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Cùng lỗi trên. Tôi chạy thật: shipping_address:{"street":"x"} → 200, lưu thành chuỗi "[object Object]". Đây là hỏng dữ liệu thầm lặng, đáng giá hơn hẳn cái expected mơ hồ ban đầu.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1052,6 +1124,16 @@
           <t>200, GET cho thấy shipping_address không đổi</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1084,6 +1166,16 @@
           <t>200 · {"message":"Profile updated"}</t>
         </is>
       </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Cùng lý do</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1116,6 +1208,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1148,6 +1250,16 @@
           <t>200 — kiểu số không thể giữ số 0 đầu</t>
         </is>
       </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1180,6 +1292,16 @@
           <t>200 — chứng minh cả 2 luật đều không được backend thực thi</t>
         </is>
       </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1212,6 +1334,16 @@
           <t>200, GET cho thấy role vẫn "user"</t>
         </is>
       </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1244,6 +1376,16 @@
           <t>200, foo không có tác dụng</t>
         </is>
       </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1276,6 +1418,16 @@
           <t>200 — luật phone không được thực thi kể cả trong ngữ cảnh hỗn hợp</t>
         </is>
       </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1308,6 +1460,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1340,6 +1502,16 @@
           <t>200 · hợp lệ theo cả đặc tả lẫn mã nguồn</t>
         </is>
       </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1372,6 +1544,16 @@
           <t>200 · hợp lệ theo cả đặc tả lẫn mã nguồn</t>
         </is>
       </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1404,6 +1586,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1436,6 +1628,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1468,6 +1670,16 @@
           <t>403 {"error":"Forbidden"} — không phải 401</t>
         </is>
       </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1500,6 +1712,16 @@
           <t>200, GET cho thấy role vẫn "user"</t>
         </is>
       </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1532,6 +1754,16 @@
           <t>200, GET cho thấy role = "0"</t>
         </is>
       </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1564,6 +1796,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1596,6 +1838,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1628,6 +1880,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1660,6 +1922,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1692,6 +1964,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Thiếu tiền điều kiện _cách tạo token_. server.js:51 ký token không có expiresIn, nên trạng thái "token hết hạn" không tồn tại trong luồng đăng nhập bình thường — bắt buộc phải tự ký bằng SECRET_KEY ở server.js:9. AI không ghi rõ điều này.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1724,6 +2006,16 @@
           <t>200 dù 0 dòng bị cập nhật (this.changes không kiểm)</t>
         </is>
       </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Thiếu bước chứng minh 0 dòng bị ghi. Đúng ra phải chỉ ra server.js:131-134 không kiểm this.changes, nên 200 ở đây không đồng nghĩa với "đã cập nhật".</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1756,6 +2048,16 @@
           <t>200, GET cho thấy role="admin" — vi phạm SEC-06</t>
         </is>
       </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1788,6 +2090,16 @@
           <t>200, lưu nguyên văn — không có enum check</t>
         </is>
       </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1820,6 +2132,16 @@
           <t>200 · lưu như chuỗi literal, bảng users còn nguyên</t>
         </is>
       </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1852,6 +2174,16 @@
           <t>200 · GET trả về nguyên văn (chỉ kiểm lưu/phản hồi, không kiểm render)</t>
         </is>
       </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1884,6 +2216,16 @@
           <t>200 · đúng 1 key message, không dư trường</t>
         </is>
       </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1916,6 +2258,16 @@
           <t>(2 assertion của TC-023: status + schema)</t>
         </is>
       </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Cùng một request, cùng expected, chỉ khác nhãn kỹ thuật. Trong Postman đây là một request với hai assertion, không phải hai TC.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1948,6 +2300,16 @@
           <t>403 · đúng 1 key error = "Forbidden"</t>
         </is>
       </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -1980,6 +2342,16 @@
           <t>200 · đủ 10 trường theo database.js:50-61</t>
         </is>
       </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2012,6 +2384,16 @@
           <t>200 · body không chứa giá trị vừa gửi</t>
         </is>
       </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -2044,6 +2426,16 @@
           <t>200 · body chứa "password":"Test1234!"</t>
         </is>
       </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Hard-code mật khẩu seed. Nếu chạy sau bất kỳ TC nào của FR-03 (reset password) thì giá trị đổi, TC fail sai.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -2076,6 +2468,16 @@
           <t>200, GET cho thấy giá trị cũ đã mất</t>
         </is>
       </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Không tách rõ setup và assert; Newman cần 2 request riêng</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -2108,6 +2510,16 @@
           <t>200 — scheme không được kiểm</t>
         </is>
       </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -2140,6 +2552,16 @@
           <t>403 · {"error":"Forbidden"} — vì "" == null là false</t>
         </is>
       </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -2170,6 +2592,16 @@
       <c r="F43" s="7" t="inlineStr">
         <is>
           <t>GET cho role="admin" nhưng payload JWT vẫn role="user"</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Không phải assertion HTTP thuần — phải giải mã payload JWT</t>
         </is>
       </c>
     </row>
@@ -2184,15 +2616,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2226,6 +2660,16 @@
           <t>Expected (status + body)</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Nhan kiem toan</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Ly do (nguoi ra soat)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -2258,6 +2702,16 @@
           <t>200 · {"message":"Order canceled successfully"}, GET → status="canceled"</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -2290,6 +2744,16 @@
           <t>404 · {"error":"Order not found"}</t>
         </is>
       </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2322,6 +2786,16 @@
           <t>404 · {"error":"Order not found"}</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Expected không quyết định được thì TC vô dụng. Tôi chạy thật: → 404 · {"error":"Order not found"}. Lý do: server.js:324 bind chuỗi vào cột INTEGER, SQLite so sánh không khớp → !order → 404.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2354,6 +2828,16 @@
           <t>404 · body là HTML của Express (404 tầng routing), không phải JSON của SUT</t>
         </is>
       </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: Express không khớp route (segment rỗng) → trả 404 mặc định của framework, không phải JSON {"error":...} của SUT. Khác biệt này quan trọng: cùng mã 404 nhưng khác schema.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2386,6 +2870,16 @@
           <t>404 — AUTOINCREMENT không bao giờ sinh id âm</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2418,6 +2912,16 @@
           <t>404 · {"error":"Order not found"}</t>
         </is>
       </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: → 404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2450,6 +2954,16 @@
           <t>404; đơn id=1 không bị hủy — SQLite không ép "1abc" thành 1</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: → 404. Đáng chú ý: SQLite không ép "1abc" thành 1, nên đơn id=1 an toàn.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2482,6 +2996,16 @@
           <t>200, status = "canceled" (không delivered) — đích ghi cứng</t>
         </is>
       </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2514,6 +3038,16 @@
           <t>404 · AUTOINCREMENT không cấp id 0</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2546,6 +3080,16 @@
           <t>200 · {"message":"Order canceled successfully"}</t>
         </is>
       </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Tiền điều kiện _"đơn id 1 tồn tại và thuộc user A"_ mong manh: id phụ thuộc thứ tự chạy của cả suite. Chạy lại lần 2 là hỏng.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2578,6 +3122,16 @@
           <t>200 · {"message":"Order canceled successfully"}</t>
         </is>
       </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Cùng lý do</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2610,6 +3164,16 @@
           <t>404 · không lỗi tràn số</t>
         </is>
       </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: → 404, không lỗi tràn</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2642,6 +3206,16 @@
           <t>404 · {"error":"Order not found"}</t>
         </is>
       </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2674,6 +3248,16 @@
           <t>200 — giả mạo không phân biệt được với token thật</t>
         </is>
       </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2706,6 +3290,16 @@
           <t>200 — chiếm trọn quyền sở hữu của id bị mạo danh</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2738,6 +3332,16 @@
           <t>403 · {"error":"Forbidden"} — không phải 401</t>
         </is>
       </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2770,6 +3374,16 @@
           <t>200 · {"message":"Order canceled successfully"}</t>
         </is>
       </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2802,6 +3416,16 @@
           <t>200 theo mã nguồn — mâu thuẫn trực tiếp với FR-10</t>
         </is>
       </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2834,6 +3458,16 @@
           <t>400 · {"error":"Cannot cancel this order."}</t>
         </is>
       </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2866,6 +3500,16 @@
           <t>400 · {"error":"Cannot cancel this order."}</t>
         </is>
       </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2898,6 +3542,16 @@
           <t>Lần 1: 200 · Lần 2: 400 — trạng thái bất biến, response thì không</t>
         </is>
       </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -2930,6 +3584,16 @@
           <t>200 — deny-list chỉ chặn delivered/canceled</t>
         </is>
       </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>TC ghi tiền điều kiện _"phải sửa DB trực tiếp"_ — tức là không thực thi được bằng Postman/Newman. Một TC API mà điều kiện tiên quyết nằm ngoài API thì không thuộc bộ test API. Đúng là database.js:78 không có CHECK, nhưng cả hai route ghi status (server.js:335 và 537-551) đều chỉ ghi 5 literal, nên trạng thái lạ không tới được qua bất kỳ API nào.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -2962,6 +3626,16 @@
           <t>400 · Invalid state transition from shipping to canceled</t>
         </is>
       </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2994,6 +3668,16 @@
           <t>200 — thoát khỏi trạng thái FR-10 gọi là kết thúc</t>
         </is>
       </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3026,6 +3710,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3058,6 +3752,16 @@
           <t>403 · {"error":"Forbidden"} — không phải 401</t>
         </is>
       </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3090,6 +3794,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3122,6 +3836,16 @@
           <t>200 — scheme không được kiểm</t>
         </is>
       </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3154,6 +3878,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -3186,6 +3920,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3218,6 +3962,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3250,6 +4004,16 @@
           <t>404 — bộ lọc user_id không bao giờ khớp</t>
         </is>
       </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3282,6 +4046,16 @@
           <t>404 · {"error":"Order not found"} — không phân biệt với "không tồn tại"</t>
         </is>
       </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -3314,6 +4088,16 @@
           <t>404 — bộ lọc ownership áp dụng cho cả admin</t>
         </is>
       </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3346,6 +4130,16 @@
           <t>404 — xử lý như chuỗi literal, không thực thi SQL</t>
         </is>
       </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -3378,6 +4172,16 @@
           <t>200 · đúng 1 key message, không có id/status</t>
         </is>
       </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -3410,6 +4214,16 @@
           <t>401 · đúng 1 key error = "Unauthorized"</t>
         </is>
       </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -3442,6 +4256,16 @@
           <t>403 · đúng 1 key error = "Forbidden"</t>
         </is>
       </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -3474,6 +4298,16 @@
           <t>Cả 2 → 404, body giống hệt từng byte (chống dò đơn)</t>
         </is>
       </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -3506,6 +4340,16 @@
           <t>Cả 2 → 400, body giống hệt từng byte</t>
         </is>
       </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -3538,6 +4382,16 @@
           <t>PUT: không có status; GET: phần tử có status="canceled"</t>
         </is>
       </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Newman cần 2 request tách biệt</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -3570,6 +4424,16 @@
           <t>200 · trả full đơn hàng — lỗ hổng của endpoint hỗ trợ</t>
         </is>
       </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -3600,6 +4464,16 @@
       <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Không có TC nào trả 500 (cả 2 callback SQLite đều bỏ qua err)</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Không phải một request. Đây là mệnh đề tổng hợp trên toàn suite, không có input, không có endpoint để gọi.</t>
         </is>
       </c>
     </row>
@@ -3614,15 +4488,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3656,6 +4532,16 @@
           <t>Expected (status + body)</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Nhan kiem toan</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Ly do (nguoi ra soat)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -3688,6 +4574,16 @@
           <t>200 · {"message":"Coupon created","id":&lt;int&gt;}</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -3720,6 +4616,16 @@
           <t>200 — không có presence check</t>
         </is>
       </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3752,6 +4658,16 @@
           <t>200 — không có non-empty check</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -3784,6 +4700,16 @@
           <t>500 · {"error":"&lt;sqlite UNIQUE text&gt;"} — không tạo dòng mới</t>
         </is>
       </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3816,6 +4742,16 @@
           <t>200; GET cho thấy type không rơi về 'percent' (DEFAULT bất hoạt)</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3848,6 +4784,16 @@
           <t>200, lưu nguyên văn — không có CHECK</t>
         </is>
       </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3880,6 +4826,16 @@
           <t>200 — không có presence check</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -3912,6 +4868,16 @@
           <t>200 · tạo được coupon</t>
         </is>
       </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: 200, tạo được coupon</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -3944,6 +4910,16 @@
           <t>200 — DEFAULT 0 cũng bất hoạt</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3976,6 +4952,16 @@
           <t>200 — không có presence check</t>
         </is>
       </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4008,6 +4994,16 @@
           <t>200 — giống hệt coupon EXPIRED được seed sẵn</t>
         </is>
       </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -4040,6 +5036,16 @@
           <t>200 — không validate định dạng ngày lúc tạo</t>
         </is>
       </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4072,6 +5078,16 @@
           <t>200; GET cho thấy lưu đúng 1 (\</t>
         </is>
       </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -4104,6 +5120,16 @@
           <t>200; GET cho thấy is_active = 1, không phải 0</t>
         </is>
       </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4136,6 +5162,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -4168,6 +5204,16 @@
           <t>200 · hợp lệ theo cả 2 nguồn</t>
         </is>
       </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4200,6 +5246,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -4232,6 +5288,16 @@
           <t>200 · hợp lệ — lưu ý biên này _bao gồm_, khác discount_value</t>
         </is>
       </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4264,6 +5330,16 @@
           <t>200; GET cho thấy 1, không phải 0</t>
         </is>
       </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -4296,6 +5372,16 @@
           <t>COV-048 · FR-17</t>
         </is>
       </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Sai kết quả. Lập luận của AI đúng một nửa: chuỗi "0" là truthy nên lọt qua \</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4328,6 +5414,16 @@
           <t>200 · hợp lệ, không bị biến đổi</t>
         </is>
       </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -4360,6 +5456,16 @@
           <t>200; lưu đúng -5 — số âm là truthy nên \</t>
         </is>
       </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -4392,6 +5498,16 @@
           <t>200 — không có chặn trên nào</t>
         </is>
       </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -4424,6 +5540,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -4456,6 +5582,16 @@
           <t>200 với id mới — AUTOINCREMENT không tái dùng id cũ</t>
         </is>
       </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -4488,6 +5624,16 @@
           <t>500 — chỉ code quyết định việc từ chối</t>
         </is>
       </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4520,6 +5666,16 @@
           <t>200 · {"message":"Coupon deleted"} — giống hệt lần xoá thật</t>
         </is>
       </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -4552,6 +5708,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4584,6 +5750,16 @@
           <t>200 — vi phạm trực tiếp SEC-03</t>
         </is>
       </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -4616,6 +5792,16 @@
           <t>200 · {"message":"Coupon deleted"}</t>
         </is>
       </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4648,6 +5834,16 @@
           <t>200 · danh sách đầy đủ y hệt admin</t>
         </is>
       </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -4680,6 +5876,16 @@
           <t>200 — nhưng theo TC-029, giả mạo thậm chí không cần thiết</t>
         </is>
       </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4712,6 +5918,16 @@
           <t>200 · lưu literal, bảng coupons còn nguyên</t>
         </is>
       </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4744,6 +5960,16 @@
           <t>200 · lưu đúng mọi giá trị cực lớn</t>
         </is>
       </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4776,6 +6002,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -4808,6 +6044,16 @@
           <t>200 · đúng 2 key message + id (int dương)</t>
         </is>
       </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -4840,6 +6086,16 @@
           <t>200 · đúng 1 key message = "Coupon deleted"</t>
         </is>
       </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -4872,6 +6128,16 @@
           <t>401 · đúng 1 key error = "Unauthorized"</t>
         </is>
       </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -4904,6 +6170,16 @@
           <t>500 · error chứa nguyên văn thông báo UNIQUE của SQLite</t>
         </is>
       </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Thiếu bước tạo SCHEMA03 trước. Chạy trên DB sạch sẽ ra 200 chứ không phải 500.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -4936,6 +6212,16 @@
           <t>Không TC nào trả 400/409 từ handler (400 chỉ đến từ bodyParser, xem TC-068)</t>
         </is>
       </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Mệnh đề tổng hợp toàn suite, không phải request</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -4968,6 +6254,16 @@
           <t>200 · body giống hệt lần xoá thật (this.changes không kiểm)</t>
         </is>
       </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -5000,6 +6296,16 @@
           <t>Lưu lần lượt 1 / 0 / -5 — 3 input "không hợp lệ" cho 3 hành vi khác nhau</t>
         </is>
       </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Không có input, không có endpoint — là bước phân tích, không phải TC</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -5032,6 +6338,16 @@
           <t>Không coupon nào của suite có is_active = 0</t>
         </is>
       </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Cùng lý do</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -5064,6 +6380,16 @@
           <t>GET không còn code:"CLEANUPTEST01" — xác thực cơ chế teardown của cả suite</t>
         </is>
       </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -5096,6 +6422,16 @@
           <t>200 · enum có 2 giá trị hợp lệ, cả hai đều phải được phủ</t>
         </is>
       </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -5128,6 +6464,16 @@
           <t>200 — cột không có NOT NULL; SQLite coi mỗi NULL là khác nhau nên UNIQUE không chặn</t>
         </is>
       </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -5160,6 +6506,16 @@
           <t>200 — UNIQUE không có COLLATE NOCASE nên là 2 mã khác nhau</t>
         </is>
       </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -5192,6 +6548,16 @@
           <t>200 — không có enum check</t>
         </is>
       </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -5224,6 +6590,16 @@
           <t>200 — DEFAULT 'percent' bất hoạt vì cột luôn được bind</t>
         </is>
       </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -5256,6 +6632,16 @@
           <t>200 — không có NOT NULL</t>
         </is>
       </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -5288,6 +6674,16 @@
           <t>200 (kỳ vọng đặc tả: từ chối)</t>
         </is>
       </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -5320,6 +6716,16 @@
           <t>200 — không có NOT NULL</t>
         </is>
       </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -5352,6 +6758,16 @@
           <t>200 · phân vùng hợp lệ ngoài biên 0</t>
         </is>
       </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -5384,6 +6800,16 @@
           <t>200 — không có NOT NULL</t>
         </is>
       </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -5416,6 +6842,16 @@
           <t>200 — lưu nguyên; new Date("") khi dùng sẽ ra Invalid Date</t>
         </is>
       </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -5448,6 +6884,16 @@
           <t>200; GET cho thấy lưu 1 (null là falsy)</t>
         </is>
       </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -5480,6 +6926,16 @@
           <t>200; GET cho thấy lưu 1</t>
         </is>
       </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -5512,6 +6968,16 @@
           <t>200 — trần khái niệm, không có tài liệu nào quy định</t>
         </is>
       </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -5544,6 +7010,16 @@
           <t>200 — vượt trần khái niệm nhưng không bị chặn</t>
         </is>
       </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -5576,6 +7052,16 @@
           <t>200; hệ quả: apply-coupon sẽ diễn giải như fixed (nhánh else)</t>
         </is>
       </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5608,6 +7094,16 @@
           <t>403 · {"error":"Forbidden"} — không phải 401</t>
         </is>
       </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -5640,6 +7136,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -5672,6 +7178,16 @@
           <t>200 — scheme không được kiểm</t>
         </is>
       </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -5704,6 +7220,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -5736,6 +7262,16 @@
           <t>403 · {"error":"Forbidden"}</t>
         </is>
       </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -5768,6 +7304,16 @@
           <t>200 — tạo được coupon rỗng: code/type/discount_value/min_order_amount/expired_at đều null, chỉ max_uses_per_user=1</t>
         </is>
       </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật (trên API 1, cùng cơ chế): 200</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -5800,6 +7346,16 @@
           <t>500 · body là HTML, không phải {"error":...} — TypeError khi destructure req.body</t>
         </is>
       </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: 500 dạng HTML, không phải JSON — do TypeError khi destructure req.body (server.js:458)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -5832,6 +7388,16 @@
           <t>400 · body là HTML, sinh bởi bodyParser trước khi vào handler</t>
         </is>
       </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật: 400 dạng HTML, sinh bởi bodyParser trước handler</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -5864,6 +7430,16 @@
           <t>401 · {"error":"Unauthorized"}</t>
         </is>
       </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -5896,6 +7472,16 @@
           <t>200 · {"message":"Coupon deleted"} dù không xoá gì — this.changes không kiểm</t>
         </is>
       </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Tôi chạy thật (tương tự API 2): 200 — vì server.js:484-487 không kiểm this.changes, xoá 0 dòng vẫn báo thành công</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -5928,6 +7514,16 @@
           <t>200 (không xoá gì) — tham số hoá, không thực thi SQL</t>
         </is>
       </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -5960,6 +7556,16 @@
           <t>200 — không có ràng buộc độ dài ở cả đặc tả lẫn schema</t>
         </is>
       </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -5992,6 +7598,16 @@
           <t>200 — không có trim/format check</t>
         </is>
       </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -6024,6 +7640,16 @@
           <t>200; lưu thành chuỗi "12345" (TEXT affinity)</t>
         </is>
       </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Cùng một gốc: AI không dám kết luận về binding kiểu. Tôi chạy mẫu discount_value:"10" và max_uses_per_user:1.5 → đều 200; riêng 1.5 lưu nguyên 1.5 (SQLite giữ REAL vì không ép được sang INTEGER không mất mát)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -6056,6 +7682,16 @@
           <t>200; lưu thành chuỗi "1" — enum bị phá hoàn toàn</t>
         </is>
       </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Cùng một gốc: AI không dám kết luận về binding kiểu. Tôi chạy mẫu discount_value:"10" và max_uses_per_user:1.5 → đều 200; riêng 1.5 lưu nguyên 1.5 (SQLite giữ REAL vì không ép được sang INTEGER không mất mát)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -6088,6 +7724,16 @@
           <t>200; lưu nguyên 10.5 (REAL) — cột INTEGER không ép vì sẽ mất mát</t>
         </is>
       </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Cùng một gốc: AI không dám kết luận về binding kiểu. Tôi chạy mẫu discount_value:"10" và max_uses_per_user:1.5 → đều 200; riêng 1.5 lưu nguyên 1.5 (SQLite giữ REAL vì không ép được sang INTEGER không mất mát)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -6120,6 +7766,16 @@
           <t>200; lưu thành 1 — boolean bị ép sang integer</t>
         </is>
       </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Cùng một gốc: AI không dám kết luận về binding kiểu. Tôi chạy mẫu discount_value:"10" và max_uses_per_user:1.5 → đều 200; riêng 1.5 lưu nguyên 1.5 (SQLite giữ REAL vì không ép được sang INTEGER không mất mát)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -6152,6 +7808,16 @@
           <t>200 — DATETIME chỉ là affinity, lưu nguyên chuỗi</t>
         </is>
       </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -6184,6 +7850,16 @@
           <t>200; lưu nguyên số 1735689600 — DATETIME chỉ là affinity</t>
         </is>
       </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Cùng một gốc: AI không dám kết luận về binding kiểu. Tôi chạy mẫu discount_value:"10" và max_uses_per_user:1.5 → đều 200; riêng 1.5 lưu nguyên 1.5 (SQLite giữ REAL vì không ép được sang INTEGER không mất mát)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -6216,6 +7892,16 @@
           <t>200; lưu nguyên 1.5 (REAL)</t>
         </is>
       </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Cùng một gốc: AI không dám kết luận về binding kiểu. Tôi chạy mẫu discount_value:"10" và max_uses_per_user:1.5 → đều 200; riêng 1.5 lưu nguyên 1.5 (SQLite giữ REAL vì không ép được sang INTEGER không mất mát)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -6248,6 +7934,16 @@
           <t>Cả hai 200, đều lưu 1 — nhưng khác cơ chế: false bị \</t>
         </is>
       </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Hai lỗi. (a) Một TC chứa hai input với hai expected khác nhau — không đánh giá pass/fail được. (b) _"giữ nguyên"_ sai: tôi chạy thật, true lưu thành 1, vì SQLite ép boolean sang integer. Nên cả true lẫn false đều ra 1, chỉ khác đường đi.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -6278,6 +7974,16 @@
       <c r="F83" s="7" t="inlineStr">
         <is>
           <t>200 — không có giới hạn trên nào được đặc tả</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>VALID - ky vong khop hanh vi probe that cua SUT; assertion PASS khi chay Newman (xem §4.4/§5.4/§6.4)</t>
         </is>
       </c>
     </row>
